--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,220 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131705253</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92261</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sydlig sotticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ischnoderma resinosum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schrad.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stora Perstorp, Stora Perstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>403534</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6160380</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Bok/Avenbok</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bok/Avenbok</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131705823</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92261</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sydlig sotticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ischnoderma resinosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schrad.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stora Perstorp, Stora Perstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>403539</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6160397</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Bok/Avenbok</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bok/Avenbok</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131705253</v>
       </c>
       <c r="B3" t="n">
-        <v>92261</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131705823</v>
       </c>
       <c r="B4" t="n">
-        <v>92261</v>
+        <v>92262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131705253</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131705823</v>
       </c>
       <c r="B4" t="n">
-        <v>92262</v>
+        <v>92265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131705253</v>
       </c>
       <c r="B3" t="n">
-        <v>92265</v>
+        <v>92271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131705823</v>
       </c>
       <c r="B4" t="n">
-        <v>92265</v>
+        <v>92271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131705253</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>92274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131705823</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>92274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131705253</v>
       </c>
       <c r="B3" t="n">
-        <v>92274</v>
+        <v>92279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131705823</v>
       </c>
       <c r="B4" t="n">
-        <v>92274</v>
+        <v>92279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131705253</v>
       </c>
       <c r="B3" t="n">
-        <v>92279</v>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131705823</v>
       </c>
       <c r="B4" t="n">
-        <v>92279</v>
+        <v>92281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131705253</v>
       </c>
       <c r="B3" t="n">
-        <v>92322</v>
+        <v>92325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131705823</v>
       </c>
       <c r="B4" t="n">
-        <v>92322</v>
+        <v>92325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4816-2025 artfynd.xlsx
+++ b/artfynd/A 4816-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103373874</v>
+        <v>131705253</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>2023</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dörröd, Sk</t>
+          <t>Stora Perstorp, Stora Perstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403664.1129129613</v>
+        <v>403534</v>
       </c>
       <c r="R2" t="n">
-        <v>6160205.792981247</v>
+        <v>6160380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,29 +754,38 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Bok/Avenbok</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bok/Avenbok</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131705253</v>
+        <v>131705823</v>
       </c>
       <c r="B3" t="n">
-        <v>92325</v>
+        <v>92379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403534</v>
+        <v>403539</v>
       </c>
       <c r="R3" t="n">
-        <v>6160380</v>
+        <v>6160397</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131705823</v>
+        <v>7072392</v>
       </c>
       <c r="B4" t="n">
-        <v>92325</v>
+        <v>96231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2023</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Perstorp, Stora Perstorp, Sk</t>
+          <t>Spörrstorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403539</v>
+        <v>403868</v>
       </c>
       <c r="R4" t="n">
-        <v>6160397</v>
+        <v>6160524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,12 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2013-11-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2013-11-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre pilevall. En del döda träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,29 +975,452 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Bok/Avenbok</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bok/Avenbok</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jacob Björnberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jacob Björnberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>BGM – tre mossor 2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103373874</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dörröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>403665</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6160206</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Haglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Haglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129924762</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Perstorp, Stora Perstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>403622</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6160521</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>83462246</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogsalm (Skyddsvärt träd), Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>403799</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6160428</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D30B72FA-CD06-494D-99CD-D722DAE7D9F5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2008-09-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2008-09-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Levenskog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Levenskog, Marit Engquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>83486890</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogsalm (Skyddsvärt träd), Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>403865</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6160518</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>088906DE-C5BB-4571-9498-EA3A6B4632DD</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2008-09-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2008-09-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Levenskog</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Levenskog, Marit Engquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
